--- a/VT_IE_SUP.xlsx
+++ b/VT_IE_SUP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BSuleimenov\Documents\GitHub\times-ireland-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8CFB296-C9B8-4A4F-95C6-29C415416C07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C979EF9-666E-4C1B-8283-003E80B0B879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="23" r:id="rId1"/>
@@ -1309,7 +1309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1489" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1497" uniqueCount="669">
   <si>
     <t>~FI_Process</t>
   </si>
@@ -3402,6 +3402,18 @@
   </si>
   <si>
     <t>ACT_BND~2023</t>
+  </si>
+  <si>
+    <t>ETSCO2</t>
+  </si>
+  <si>
+    <t>NOETSCO2</t>
+  </si>
+  <si>
+    <t>All emissions under EU-ETS</t>
+  </si>
+  <si>
+    <t>All emissions not included in EU ETS</t>
   </si>
 </sst>
 </file>
@@ -7737,7 +7749,7 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>1</xdr:col>
-          <xdr:colOff>28575</xdr:colOff>
+          <xdr:colOff>30480</xdr:colOff>
           <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
@@ -8205,17 +8217,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C0DC7F3-E799-4282-82F0-A564D9B9FE0C}">
   <sheetPr codeName="Sheet16"/>
   <dimension ref="A1:Z99"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="6" width="14.140625" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" customWidth="1"/>
-    <col min="8" max="10" width="8.140625" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" customWidth="1"/>
-    <col min="12" max="12" width="8.140625" customWidth="1"/>
+    <col min="1" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="6" width="14.109375" customWidth="1"/>
+    <col min="7" max="7" width="12.109375" customWidth="1"/>
+    <col min="8" max="10" width="8.109375" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" customWidth="1"/>
+    <col min="12" max="12" width="8.109375" customWidth="1"/>
     <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="11.28515625" customWidth="1"/>
-    <col min="15" max="15" width="13.28515625" customWidth="1"/>
+    <col min="14" max="14" width="11.33203125" customWidth="1"/>
+    <col min="15" max="15" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
@@ -11057,25 +11069,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:W79"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="3.85546875" style="23" customWidth="1"/>
-    <col min="2" max="2" width="9.42578125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" style="23" customWidth="1"/>
-    <col min="4" max="4" width="31.85546875" style="23" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="23" customWidth="1"/>
-    <col min="6" max="13" width="10.85546875" style="23" customWidth="1"/>
-    <col min="14" max="14" width="12.85546875" style="23" customWidth="1"/>
+    <col min="1" max="1" width="3.88671875" style="23" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" style="23" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" style="23" customWidth="1"/>
+    <col min="4" max="4" width="31.88671875" style="23" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" style="23" customWidth="1"/>
+    <col min="6" max="13" width="10.88671875" style="23" customWidth="1"/>
+    <col min="14" max="14" width="12.88671875" style="23" customWidth="1"/>
     <col min="15" max="16" width="13" style="23" customWidth="1"/>
-    <col min="17" max="17" width="21.85546875" style="23" customWidth="1"/>
-    <col min="18" max="18" width="29.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="19" max="22" width="9.140625" style="23"/>
-    <col min="23" max="23" width="14.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="29.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="23"/>
+    <col min="17" max="17" width="21.88671875" style="23" customWidth="1"/>
+    <col min="18" max="18" width="29.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="19" max="22" width="9.109375" style="23"/>
+    <col min="23" max="23" width="14.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="29.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.109375" style="23"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" ht="18.75">
+    <row r="2" spans="2:12" ht="18">
       <c r="B2" s="3" t="s">
         <v>81</v>
       </c>
@@ -11127,7 +11139,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="2:12" ht="32.65" customHeight="1" thickBot="1">
+    <row r="4" spans="2:12" ht="32.700000000000003" customHeight="1" thickBot="1">
       <c r="B4" s="9" t="s">
         <v>514</v>
       </c>
@@ -11825,7 +11837,7 @@
       <c r="K21" s="50"/>
       <c r="L21" s="22"/>
     </row>
-    <row r="22" spans="2:18" ht="18.75">
+    <row r="22" spans="2:18" ht="18">
       <c r="B22" s="3" t="s">
         <v>81</v>
       </c>
@@ -11887,7 +11899,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="2:18" ht="26.25" thickBot="1">
+    <row r="24" spans="2:18" ht="28.2" thickBot="1">
       <c r="B24" s="9" t="s">
         <v>514</v>
       </c>
@@ -11985,7 +11997,7 @@
       <c r="L26" s="22"/>
       <c r="M26" s="22"/>
     </row>
-    <row r="27" spans="2:18" ht="26.25">
+    <row r="27" spans="2:18" ht="25.8">
       <c r="B27" s="3" t="s">
         <v>109</v>
       </c>
@@ -12044,7 +12056,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="29" spans="2:18" ht="24.95" customHeight="1" thickBot="1">
+    <row r="29" spans="2:18" ht="24.9" customHeight="1" thickBot="1">
       <c r="B29" s="9" t="s">
         <v>514</v>
       </c>
@@ -12083,7 +12095,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="30" spans="2:18" ht="15.75" thickBot="1">
+    <row r="30" spans="2:18" ht="15" thickBot="1">
       <c r="B30" s="43" t="str">
         <f t="shared" ref="B30" si="4">B13</f>
         <v>IE,National</v>
@@ -12442,7 +12454,7 @@
       <c r="I39" s="24"/>
       <c r="J39" s="24"/>
     </row>
-    <row r="40" spans="2:23" ht="18.75">
+    <row r="40" spans="2:23" ht="18">
       <c r="B40" s="3" t="s">
         <v>82</v>
       </c>
@@ -12513,7 +12525,7 @@
       <c r="V41"/>
       <c r="W41"/>
     </row>
-    <row r="42" spans="2:23" ht="26.65" customHeight="1" thickBot="1">
+    <row r="42" spans="2:23" ht="26.7" customHeight="1" thickBot="1">
       <c r="B42" s="8" t="s">
         <v>514</v>
       </c>
@@ -12804,7 +12816,7 @@
       <c r="V46"/>
       <c r="W46"/>
     </row>
-    <row r="47" spans="2:23" ht="15.75" thickBot="1">
+    <row r="47" spans="2:23" ht="15" thickBot="1">
       <c r="B47" s="46" t="s">
         <v>79</v>
       </c>
@@ -13079,7 +13091,7 @@
       <c r="P51" s="51"/>
       <c r="R51" s="25"/>
     </row>
-    <row r="52" spans="2:18" ht="15.75" thickBot="1">
+    <row r="52" spans="2:18" ht="15" thickBot="1">
       <c r="B52" s="46" t="s">
         <v>79</v>
       </c>
@@ -13339,7 +13351,7 @@
       <c r="P56" s="51"/>
       <c r="R56" s="25"/>
     </row>
-    <row r="57" spans="2:18" ht="15.75" thickBot="1">
+    <row r="57" spans="2:18" ht="15" thickBot="1">
       <c r="B57" s="46" t="s">
         <v>79</v>
       </c>
@@ -13614,7 +13626,7 @@
       <c r="P61" s="51"/>
       <c r="R61" s="25"/>
     </row>
-    <row r="62" spans="2:18" ht="15.75" thickBot="1">
+    <row r="62" spans="2:18" ht="15" thickBot="1">
       <c r="B62" s="48" t="s">
         <v>79</v>
       </c>
@@ -13662,7 +13674,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="66" spans="4:13" ht="15.75" thickBot="1">
+    <row r="66" spans="4:13" ht="15" thickBot="1">
       <c r="D66" s="23" t="s">
         <v>650</v>
       </c>
@@ -13911,23 +13923,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7"/>
   <dimension ref="B2:O35"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="12.5703125" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" customWidth="1"/>
-    <col min="4" max="4" width="34.85546875" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5546875" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
+    <col min="4" max="4" width="34.88671875" customWidth="1"/>
+    <col min="5" max="5" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="15.5703125" customWidth="1"/>
-    <col min="10" max="10" width="20.7109375" customWidth="1"/>
+    <col min="9" max="9" width="15.5546875" customWidth="1"/>
+    <col min="10" max="10" width="20.6640625" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
     <col min="12" max="12" width="14" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" customWidth="1"/>
-    <col min="17" max="17" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5546875" customWidth="1"/>
+    <col min="17" max="17" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="29.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" ht="18.75">
+    <row r="2" spans="2:15" ht="18">
       <c r="B2" s="3" t="s">
         <v>50</v>
       </c>
@@ -13984,7 +13996,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="4" spans="2:15" ht="15.75" thickBot="1">
+    <row r="4" spans="2:15" ht="15" thickBot="1">
       <c r="B4" s="9" t="s">
         <v>515</v>
       </c>
@@ -14254,7 +14266,7 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" spans="2:15" ht="18.75">
+    <row r="13" spans="2:15" ht="18">
       <c r="B13" s="3" t="s">
         <v>55</v>
       </c>
@@ -14273,7 +14285,7 @@
       <c r="M13" s="2"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" spans="2:15" ht="25.5">
+    <row r="14" spans="2:15" ht="27.6">
       <c r="B14" s="11" t="s">
         <v>513</v>
       </c>
@@ -14303,7 +14315,7 @@
       <c r="N14" s="2"/>
       <c r="O14" s="105"/>
     </row>
-    <row r="15" spans="2:15" ht="15.75" thickBot="1">
+    <row r="15" spans="2:15" ht="15" thickBot="1">
       <c r="B15" s="8" t="s">
         <v>515</v>
       </c>
@@ -14610,21 +14622,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="B2:R42"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="22"/>
-    <col min="2" max="2" width="12.85546875" style="22" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" style="22" customWidth="1"/>
-    <col min="4" max="4" width="69.7109375" style="22" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" style="22" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.140625" style="22" customWidth="1"/>
-    <col min="7" max="9" width="9.140625" style="22"/>
-    <col min="10" max="10" width="14.140625" style="22" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="39.5703125" style="22" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="22"/>
+    <col min="1" max="1" width="9.109375" style="22"/>
+    <col min="2" max="2" width="12.88671875" style="22" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" style="22" customWidth="1"/>
+    <col min="4" max="4" width="69.6640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" style="22" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.109375" style="22" customWidth="1"/>
+    <col min="7" max="9" width="9.109375" style="22"/>
+    <col min="10" max="10" width="14.109375" style="22" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="39.5546875" style="22" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="9.109375" style="22"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="18.75">
+    <row r="2" spans="2:18" ht="18">
       <c r="B2" s="3" t="s">
         <v>131</v>
       </c>
@@ -14656,7 +14668,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="13.5" thickBot="1">
+    <row r="4" spans="2:18" ht="28.2" thickBot="1">
       <c r="B4" s="8" t="s">
         <v>514</v>
       </c>
@@ -14674,7 +14686,7 @@
       </c>
       <c r="G4" s="8"/>
     </row>
-    <row r="5" spans="2:18" ht="15">
+    <row r="5" spans="2:18" ht="14.4">
       <c r="B5" s="21" t="str">
         <f>Processes!C51</f>
         <v>IE,National</v>
@@ -14699,7 +14711,7 @@
       </c>
       <c r="R5" s="23"/>
     </row>
-    <row r="6" spans="2:18" ht="15">
+    <row r="6" spans="2:18" ht="14.4">
       <c r="B6" s="21" t="str">
         <f>Processes!C54</f>
         <v>IE,National</v>
@@ -14722,7 +14734,7 @@
       <c r="G6" s="480"/>
       <c r="R6" s="23"/>
     </row>
-    <row r="7" spans="2:18" ht="15">
+    <row r="7" spans="2:18" ht="14.4">
       <c r="B7" s="21" t="str">
         <f>Processes!C60</f>
         <v>IE,National</v>
@@ -14745,7 +14757,7 @@
       <c r="G7" s="480"/>
       <c r="R7" s="23"/>
     </row>
-    <row r="8" spans="2:18" ht="15">
+    <row r="8" spans="2:18" ht="14.4">
       <c r="B8" s="21" t="str">
         <f>Processes!C66</f>
         <v>IE,National</v>
@@ -14768,7 +14780,7 @@
       <c r="G8" s="480"/>
       <c r="R8" s="23"/>
     </row>
-    <row r="9" spans="2:18" ht="15">
+    <row r="9" spans="2:18" ht="14.4">
       <c r="B9" s="21" t="str">
         <f>Processes!C69</f>
         <v>IE,National</v>
@@ -14791,7 +14803,7 @@
       <c r="G9" s="480"/>
       <c r="R9" s="23"/>
     </row>
-    <row r="10" spans="2:18" ht="15">
+    <row r="10" spans="2:18" ht="14.4">
       <c r="B10" s="21" t="str">
         <f>Processes!C57</f>
         <v>IE,National</v>
@@ -14814,7 +14826,7 @@
       <c r="G10" s="480"/>
       <c r="R10" s="23"/>
     </row>
-    <row r="11" spans="2:18" ht="15">
+    <row r="11" spans="2:18" ht="14.4">
       <c r="B11" s="21" t="str">
         <f>Processes!C72</f>
         <v>IE,National</v>
@@ -14837,7 +14849,7 @@
       <c r="G11" s="480"/>
       <c r="R11" s="23"/>
     </row>
-    <row r="12" spans="2:18" ht="15">
+    <row r="12" spans="2:18" ht="14.4">
       <c r="B12" s="21" t="str">
         <f>Processes!C75</f>
         <v>IE,National</v>
@@ -14860,7 +14872,7 @@
       <c r="G12" s="480"/>
       <c r="R12" s="23"/>
     </row>
-    <row r="13" spans="2:18" ht="15">
+    <row r="13" spans="2:18" ht="14.4">
       <c r="B13" s="21" t="str">
         <f>Processes!C63</f>
         <v>IE,National</v>
@@ -14883,7 +14895,7 @@
       <c r="G13" s="480"/>
       <c r="R13" s="23"/>
     </row>
-    <row r="14" spans="2:18" ht="15">
+    <row r="14" spans="2:18" ht="14.4">
       <c r="B14" s="45" t="str">
         <f>Processes!C78</f>
         <v>IE,National</v>
@@ -14906,7 +14918,7 @@
       <c r="G14" s="480"/>
       <c r="R14" s="23"/>
     </row>
-    <row r="15" spans="2:18" ht="15">
+    <row r="15" spans="2:18" ht="14.4">
       <c r="B15" s="21" t="str">
         <f>Processes!C52</f>
         <v>IE,National</v>
@@ -14929,7 +14941,7 @@
       <c r="G15" s="480"/>
       <c r="R15" s="23"/>
     </row>
-    <row r="16" spans="2:18" ht="15">
+    <row r="16" spans="2:18" ht="14.4">
       <c r="B16" s="21" t="str">
         <f>Processes!C55</f>
         <v>IE,National</v>
@@ -14952,7 +14964,7 @@
       <c r="G16" s="480"/>
       <c r="R16" s="23"/>
     </row>
-    <row r="17" spans="2:18" ht="15">
+    <row r="17" spans="2:18" ht="14.4">
       <c r="B17" s="21" t="str">
         <f>Processes!C61</f>
         <v>IE,National</v>
@@ -14975,7 +14987,7 @@
       <c r="G17" s="480"/>
       <c r="R17" s="23"/>
     </row>
-    <row r="18" spans="2:18" ht="15">
+    <row r="18" spans="2:18" ht="14.4">
       <c r="B18" s="21" t="str">
         <f>Processes!C67</f>
         <v>IE,National</v>
@@ -14998,7 +15010,7 @@
       <c r="G18" s="480"/>
       <c r="R18" s="23"/>
     </row>
-    <row r="19" spans="2:18" ht="15">
+    <row r="19" spans="2:18" ht="14.4">
       <c r="B19" s="21" t="str">
         <f>Processes!C70</f>
         <v>IE,National</v>
@@ -15021,7 +15033,7 @@
       <c r="G19" s="480"/>
       <c r="R19" s="23"/>
     </row>
-    <row r="20" spans="2:18" ht="15">
+    <row r="20" spans="2:18" ht="14.4">
       <c r="B20" s="21" t="str">
         <f>Processes!C58</f>
         <v>IE,National</v>
@@ -15364,7 +15376,7 @@
       <c r="F36" s="50"/>
       <c r="G36" s="190"/>
     </row>
-    <row r="37" spans="2:7" ht="15">
+    <row r="37" spans="2:7" ht="14.4">
       <c r="B37"/>
       <c r="C37"/>
       <c r="D37"/>
@@ -15372,7 +15384,7 @@
       <c r="F37"/>
       <c r="G37"/>
     </row>
-    <row r="38" spans="2:7" ht="15">
+    <row r="38" spans="2:7" ht="14.4">
       <c r="B38"/>
       <c r="C38"/>
       <c r="D38"/>
@@ -15380,7 +15392,7 @@
       <c r="F38"/>
       <c r="G38"/>
     </row>
-    <row r="39" spans="2:7" ht="15">
+    <row r="39" spans="2:7" ht="14.4">
       <c r="B39"/>
       <c r="C39"/>
       <c r="D39"/>
@@ -15388,7 +15400,7 @@
       <c r="F39"/>
       <c r="G39"/>
     </row>
-    <row r="40" spans="2:7" ht="15">
+    <row r="40" spans="2:7" ht="14.4">
       <c r="B40"/>
       <c r="C40"/>
       <c r="D40"/>
@@ -15396,7 +15408,7 @@
       <c r="F40"/>
       <c r="G40"/>
     </row>
-    <row r="41" spans="2:7" ht="15">
+    <row r="41" spans="2:7" ht="14.4">
       <c r="B41"/>
       <c r="C41"/>
       <c r="D41"/>
@@ -15404,7 +15416,7 @@
       <c r="F41"/>
       <c r="G41"/>
     </row>
-    <row r="42" spans="2:7" ht="15">
+    <row r="42" spans="2:7" ht="14.4">
       <c r="B42"/>
       <c r="C42"/>
       <c r="D42"/>
@@ -15425,21 +15437,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet9"/>
   <dimension ref="B1:AD35"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="23"/>
-    <col min="2" max="2" width="9.7109375" style="23" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" style="23" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="23"/>
+    <col min="2" max="2" width="9.6640625" style="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5546875" style="23" customWidth="1"/>
     <col min="4" max="4" width="17" style="23" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.28515625" style="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" style="23"/>
-    <col min="7" max="20" width="9.28515625" style="25" customWidth="1"/>
-    <col min="21" max="23" width="9.28515625" style="23" customWidth="1"/>
-    <col min="24" max="24" width="28.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="9.140625" style="23"/>
-    <col min="26" max="26" width="13.5703125" style="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" style="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" style="23"/>
+    <col min="7" max="20" width="9.33203125" style="25" customWidth="1"/>
+    <col min="21" max="23" width="9.33203125" style="23" customWidth="1"/>
+    <col min="24" max="24" width="28.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.109375" style="23"/>
+    <col min="26" max="26" width="13.5546875" style="23" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="17" style="23" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="23"/>
+    <col min="28" max="16384" width="9.109375" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:26">
@@ -15447,7 +15459,7 @@
       <c r="S1" s="23"/>
       <c r="T1" s="23"/>
     </row>
-    <row r="2" spans="2:26" ht="18.75">
+    <row r="2" spans="2:26" ht="18">
       <c r="B2" s="112" t="s">
         <v>145</v>
       </c>
@@ -15472,7 +15484,7 @@
       <c r="S2" s="124"/>
       <c r="T2" s="23"/>
     </row>
-    <row r="3" spans="2:26" ht="25.5">
+    <row r="3" spans="2:26" ht="27.6">
       <c r="B3" s="110" t="s">
         <v>513</v>
       </c>
@@ -16193,29 +16205,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet10"/>
   <dimension ref="B2:T36"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="23"/>
-    <col min="2" max="2" width="13.28515625" style="23" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" style="23" customWidth="1"/>
-    <col min="4" max="4" width="46.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" style="23" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="23"/>
+    <col min="2" max="2" width="13.33203125" style="23" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" style="23" customWidth="1"/>
+    <col min="4" max="4" width="46.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" style="23" customWidth="1"/>
     <col min="6" max="6" width="10" style="23" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.28515625" style="23" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" style="23" customWidth="1"/>
+    <col min="7" max="7" width="9.33203125" style="23" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.109375" style="23" customWidth="1"/>
     <col min="10" max="10" width="11" style="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="10.140625" style="23" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" style="23" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="18" max="21" width="10.28515625" style="23" customWidth="1"/>
-    <col min="22" max="22" width="9.140625" style="23"/>
+    <col min="11" max="15" width="10.109375" style="23" customWidth="1"/>
+    <col min="16" max="16" width="9.6640625" style="23" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="18" max="21" width="10.33203125" style="23" customWidth="1"/>
+    <col min="22" max="22" width="9.109375" style="23"/>
     <col min="23" max="23" width="12" style="23" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="26.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="23"/>
+    <col min="24" max="24" width="26.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.109375" style="23"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:20" ht="18.75">
+    <row r="2" spans="2:20" ht="18">
       <c r="B2" s="3" t="s">
         <v>57</v>
       </c>
@@ -16230,7 +16242,7 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" spans="2:20">
+    <row r="3" spans="2:20" ht="27.6">
       <c r="B3" s="11" t="s">
         <v>513</v>
       </c>
@@ -16281,7 +16293,7 @@
       </c>
       <c r="R3"/>
     </row>
-    <row r="4" spans="2:20" ht="15.75" thickBot="1">
+    <row r="4" spans="2:20" ht="15" thickBot="1">
       <c r="B4" s="13" t="s">
         <v>515</v>
       </c>
@@ -17089,14 +17101,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6297AC73-3506-47A0-A87E-4DEE2B4424AC}">
   <sheetPr codeName="Sheet11"/>
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="23"/>
-    <col min="2" max="2" width="18.85546875" style="23" customWidth="1"/>
-    <col min="3" max="5" width="9.140625" style="23"/>
-    <col min="6" max="6" width="15.5703125" style="23" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="23"/>
+    <col min="2" max="2" width="18.88671875" style="23" customWidth="1"/>
+    <col min="3" max="5" width="9.109375" style="23"/>
+    <col min="6" max="6" width="15.5546875" style="23" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" style="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="23"/>
+    <col min="8" max="16384" width="9.109375" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -17113,7 +17125,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" thickBot="1">
+    <row r="5" spans="1:7" ht="15" thickBot="1">
       <c r="B5" s="163" t="s">
         <v>16</v>
       </c>
@@ -17202,7 +17214,7 @@
       </c>
       <c r="G16"/>
     </row>
-    <row r="17" spans="2:7" ht="15.75" thickBot="1">
+    <row r="17" spans="2:7" ht="15" thickBot="1">
       <c r="B17" s="163" t="s">
         <v>16</v>
       </c>
@@ -17322,9 +17334,9 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:Z57"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="20.28515625" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" customWidth="1"/>
     <col min="2" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -17369,7 +17381,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="15.75" thickBot="1">
+    <row r="3" spans="1:22" ht="15" thickBot="1">
       <c r="A3" s="69" t="s">
         <v>92</v>
       </c>
@@ -17404,7 +17416,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" spans="1:22" ht="15.75" thickBot="1">
+    <row r="5" spans="1:22" ht="15" thickBot="1">
       <c r="A5" s="75" t="s">
         <v>96</v>
       </c>
@@ -17414,7 +17426,7 @@
       </c>
       <c r="J5" s="23"/>
     </row>
-    <row r="6" spans="1:22" ht="15.75" thickBot="1">
+    <row r="6" spans="1:22" ht="15" thickBot="1">
       <c r="A6" s="77"/>
       <c r="B6" s="78" t="s">
         <v>18</v>
@@ -17457,7 +17469,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="1:22" ht="15.75" thickBot="1">
+    <row r="7" spans="1:22" ht="15" thickBot="1">
       <c r="A7" s="80" t="s">
         <v>98</v>
       </c>
@@ -17510,7 +17522,7 @@
       <c r="R7" s="84"/>
       <c r="S7" s="84"/>
     </row>
-    <row r="8" spans="1:22" ht="15.75" thickBot="1">
+    <row r="8" spans="1:22" ht="15" thickBot="1">
       <c r="A8" s="80" t="s">
         <v>98</v>
       </c>
@@ -17563,7 +17575,7 @@
       <c r="R8" s="84"/>
       <c r="S8" s="84"/>
     </row>
-    <row r="9" spans="1:22" ht="15.75" thickBot="1">
+    <row r="9" spans="1:22" ht="15" thickBot="1">
       <c r="A9" s="80" t="s">
         <v>103</v>
       </c>
@@ -17616,7 +17628,7 @@
       <c r="R9" s="84"/>
       <c r="S9" s="84"/>
     </row>
-    <row r="10" spans="1:22" ht="15.75" thickBot="1">
+    <row r="10" spans="1:22" ht="15" thickBot="1">
       <c r="A10" s="80" t="s">
         <v>103</v>
       </c>
@@ -17669,7 +17681,7 @@
       <c r="R10" s="84"/>
       <c r="S10" s="84"/>
     </row>
-    <row r="11" spans="1:22" ht="15.75" thickBot="1">
+    <row r="11" spans="1:22" ht="15" thickBot="1">
       <c r="A11" s="80" t="s">
         <v>83</v>
       </c>
@@ -17716,7 +17728,7 @@
         <v>5.4816516360000005</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="15.75" thickBot="1">
+    <row r="12" spans="1:22" ht="15" thickBot="1">
       <c r="A12" s="80" t="s">
         <v>83</v>
       </c>
@@ -17763,7 +17775,7 @@
         <v>13.781408235406515</v>
       </c>
     </row>
-    <row r="13" spans="1:22" ht="15.75" thickBot="1">
+    <row r="13" spans="1:22" ht="15" thickBot="1">
       <c r="A13" s="80" t="s">
         <v>84</v>
       </c>
@@ -17810,7 +17822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:22" ht="15.75" thickBot="1">
+    <row r="14" spans="1:22" ht="15" thickBot="1">
       <c r="A14" s="80" t="s">
         <v>84</v>
       </c>
@@ -17863,7 +17875,7 @@
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
     </row>
-    <row r="16" spans="1:22" ht="15.75" thickBot="1">
+    <row r="16" spans="1:22" ht="15" thickBot="1">
       <c r="A16" s="75" t="s">
         <v>100</v>
       </c>
@@ -17879,7 +17891,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="17" spans="1:26" ht="15.75" thickBot="1">
+    <row r="17" spans="1:26" ht="15" thickBot="1">
       <c r="A17" s="77"/>
       <c r="B17" s="78" t="s">
         <v>18</v>
@@ -17949,7 +17961,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="18" spans="1:26" ht="15.75" thickBot="1">
+    <row r="18" spans="1:26" ht="15" thickBot="1">
       <c r="A18" s="80" t="s">
         <v>98</v>
       </c>
@@ -17998,7 +18010,7 @@
       <c r="O18" s="23"/>
       <c r="P18" s="87"/>
     </row>
-    <row r="19" spans="1:26" ht="15.75" thickBot="1">
+    <row r="19" spans="1:26" ht="15" thickBot="1">
       <c r="A19" s="80" t="s">
         <v>98</v>
       </c>
@@ -18085,7 +18097,7 @@
         <v>2.6576562288177672</v>
       </c>
     </row>
-    <row r="20" spans="1:26" ht="15.75" thickBot="1">
+    <row r="20" spans="1:26" ht="15" thickBot="1">
       <c r="A20" s="80" t="s">
         <v>103</v>
       </c>
@@ -18132,7 +18144,7 @@
         <v>144.52992698400001</v>
       </c>
     </row>
-    <row r="21" spans="1:26" ht="15.75" thickBot="1">
+    <row r="21" spans="1:26" ht="15" thickBot="1">
       <c r="A21" s="80" t="s">
         <v>103</v>
       </c>
@@ -18219,7 +18231,7 @@
         <v>5.4463236801828891</v>
       </c>
     </row>
-    <row r="22" spans="1:26" ht="15.75" thickBot="1">
+    <row r="22" spans="1:26" ht="15" thickBot="1">
       <c r="A22" s="80" t="s">
         <v>83</v>
       </c>
@@ -18267,7 +18279,7 @@
       </c>
       <c r="P22" s="87"/>
     </row>
-    <row r="23" spans="1:26" ht="15.75" thickBot="1">
+    <row r="23" spans="1:26" ht="15" thickBot="1">
       <c r="A23" s="80" t="s">
         <v>83</v>
       </c>
@@ -18354,7 +18366,7 @@
         <v>12.446066141998699</v>
       </c>
     </row>
-    <row r="24" spans="1:26" ht="15.75" thickBot="1">
+    <row r="24" spans="1:26" ht="15" thickBot="1">
       <c r="A24" s="80" t="s">
         <v>84</v>
       </c>
@@ -18401,7 +18413,7 @@
         <v>3.8660492520000003</v>
       </c>
     </row>
-    <row r="25" spans="1:26" ht="15.75" thickBot="1">
+    <row r="25" spans="1:26" ht="15" thickBot="1">
       <c r="A25" s="80" t="s">
         <v>84</v>
       </c>
@@ -18488,7 +18500,7 @@
         <v>24.555246283161342</v>
       </c>
     </row>
-    <row r="26" spans="1:26" ht="15.75" thickBot="1">
+    <row r="26" spans="1:26" ht="15" thickBot="1">
       <c r="A26" s="75" t="s">
         <v>102</v>
       </c>
@@ -18505,7 +18517,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="27" spans="1:26" ht="15.75" thickBot="1">
+    <row r="27" spans="1:26" ht="15" thickBot="1">
       <c r="A27" s="90"/>
       <c r="B27" s="78" t="s">
         <v>18</v>
@@ -18575,7 +18587,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="28" spans="1:26" ht="15.75" thickBot="1">
+    <row r="28" spans="1:26" ht="15" thickBot="1">
       <c r="A28" s="80" t="s">
         <v>98</v>
       </c>
@@ -18623,7 +18635,7 @@
       </c>
       <c r="P28" s="87"/>
     </row>
-    <row r="29" spans="1:26" ht="15.75" thickBot="1">
+    <row r="29" spans="1:26" ht="15" thickBot="1">
       <c r="A29" s="80" t="s">
         <v>98</v>
       </c>
@@ -18710,7 +18722,7 @@
         <v>3.425007675166559</v>
       </c>
     </row>
-    <row r="30" spans="1:26" ht="15.75" thickBot="1">
+    <row r="30" spans="1:26" ht="15" thickBot="1">
       <c r="A30" s="80" t="s">
         <v>103</v>
       </c>
@@ -18757,7 +18769,7 @@
         <v>236.79263826000002</v>
       </c>
     </row>
-    <row r="31" spans="1:26" ht="15.75" thickBot="1">
+    <row r="31" spans="1:26" ht="15" thickBot="1">
       <c r="A31" s="80" t="s">
         <v>103</v>
       </c>
@@ -18844,7 +18856,7 @@
         <v>6.8687312392684552</v>
       </c>
     </row>
-    <row r="32" spans="1:26" ht="15.75" thickBot="1">
+    <row r="32" spans="1:26" ht="15" thickBot="1">
       <c r="A32" s="80" t="s">
         <v>83</v>
       </c>
@@ -18892,7 +18904,7 @@
       </c>
       <c r="P32" s="87"/>
     </row>
-    <row r="33" spans="1:26" ht="15.75" thickBot="1">
+    <row r="33" spans="1:26" ht="15" thickBot="1">
       <c r="A33" s="80" t="s">
         <v>83</v>
       </c>
@@ -18979,7 +18991,7 @@
         <v>14.991427037204447</v>
       </c>
     </row>
-    <row r="34" spans="1:26" ht="15.75" thickBot="1">
+    <row r="34" spans="1:26" ht="15" thickBot="1">
       <c r="A34" s="80" t="s">
         <v>84</v>
       </c>
@@ -19026,7 +19038,7 @@
         <v>4.3794765360000003</v>
       </c>
     </row>
-    <row r="35" spans="1:26" ht="15.75" thickBot="1">
+    <row r="35" spans="1:26" ht="15" thickBot="1">
       <c r="A35" s="80" t="s">
         <v>84</v>
       </c>
@@ -19123,7 +19135,7 @@
       <c r="M36" s="57"/>
       <c r="N36" s="57"/>
     </row>
-    <row r="37" spans="1:26" ht="15.75" thickBot="1">
+    <row r="37" spans="1:26" ht="15" thickBot="1">
       <c r="A37" s="75" t="s">
         <v>104</v>
       </c>
@@ -19143,7 +19155,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="38" spans="1:26" ht="15.75" thickBot="1">
+    <row r="38" spans="1:26" ht="15" thickBot="1">
       <c r="A38" s="77"/>
       <c r="B38" s="78" t="s">
         <v>18</v>
@@ -19213,7 +19225,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="39" spans="1:26" ht="15.75" thickBot="1">
+    <row r="39" spans="1:26" ht="15" thickBot="1">
       <c r="A39" s="80" t="s">
         <v>98</v>
       </c>
@@ -19261,7 +19273,7 @@
       </c>
       <c r="P39" s="87"/>
     </row>
-    <row r="40" spans="1:26" ht="15.75" thickBot="1">
+    <row r="40" spans="1:26" ht="15" thickBot="1">
       <c r="A40" s="80" t="s">
         <v>98</v>
       </c>
@@ -19348,7 +19360,7 @@
         <v>3.0319740075244952</v>
       </c>
     </row>
-    <row r="41" spans="1:26" ht="15.75" thickBot="1">
+    <row r="41" spans="1:26" ht="15" thickBot="1">
       <c r="A41" s="80" t="s">
         <v>103</v>
       </c>
@@ -19395,7 +19407,7 @@
         <v>17.883748728000004</v>
       </c>
     </row>
-    <row r="42" spans="1:26" ht="15.75" thickBot="1">
+    <row r="42" spans="1:26" ht="15" thickBot="1">
       <c r="A42" s="80" t="s">
         <v>103</v>
       </c>
@@ -19482,7 +19494,7 @@
         <v>6.1949592375963451</v>
       </c>
     </row>
-    <row r="43" spans="1:26" ht="15.75" thickBot="1">
+    <row r="43" spans="1:26" ht="15" thickBot="1">
       <c r="A43" s="80" t="s">
         <v>83</v>
       </c>
@@ -19530,7 +19542,7 @@
       </c>
       <c r="P43" s="87"/>
     </row>
-    <row r="44" spans="1:26" ht="15.75" thickBot="1">
+    <row r="44" spans="1:26" ht="15" thickBot="1">
       <c r="A44" s="80" t="s">
         <v>83</v>
       </c>
@@ -19617,7 +19629,7 @@
         <v>18.45386649024168</v>
       </c>
     </row>
-    <row r="45" spans="1:26" ht="15.75" thickBot="1">
+    <row r="45" spans="1:26" ht="15" thickBot="1">
       <c r="A45" s="80" t="s">
         <v>84</v>
       </c>
@@ -19664,7 +19676,7 @@
         <v>4.602800448</v>
       </c>
     </row>
-    <row r="46" spans="1:26" ht="15.75" thickBot="1">
+    <row r="46" spans="1:26" ht="15" thickBot="1">
       <c r="A46" s="80" t="s">
         <v>84</v>
       </c>
@@ -19761,7 +19773,7 @@
       <c r="M47" s="57"/>
       <c r="N47" s="57"/>
     </row>
-    <row r="48" spans="1:26" ht="15.75" thickBot="1">
+    <row r="48" spans="1:26" ht="15" thickBot="1">
       <c r="A48" s="75" t="s">
         <v>105</v>
       </c>
@@ -19781,7 +19793,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="49" spans="1:26" ht="15.75" thickBot="1">
+    <row r="49" spans="1:26" ht="15" thickBot="1">
       <c r="A49" s="77"/>
       <c r="B49" s="78" t="s">
         <v>18</v>
@@ -19851,7 +19863,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="50" spans="1:26" ht="15.75" thickBot="1">
+    <row r="50" spans="1:26" ht="15" thickBot="1">
       <c r="A50" s="80" t="s">
         <v>98</v>
       </c>
@@ -19899,7 +19911,7 @@
       </c>
       <c r="P50" s="87"/>
     </row>
-    <row r="51" spans="1:26" ht="15.75" thickBot="1">
+    <row r="51" spans="1:26" ht="15" thickBot="1">
       <c r="A51" s="80" t="s">
         <v>98</v>
       </c>
@@ -19986,7 +19998,7 @@
         <v>3.949052565355978</v>
       </c>
     </row>
-    <row r="52" spans="1:26" ht="15.75" thickBot="1">
+    <row r="52" spans="1:26" ht="15" thickBot="1">
       <c r="A52" s="80" t="s">
         <v>103</v>
       </c>
@@ -20033,7 +20045,7 @@
         <v>110.14646000400001</v>
       </c>
     </row>
-    <row r="53" spans="1:26" ht="15.75" thickBot="1">
+    <row r="53" spans="1:26" ht="15" thickBot="1">
       <c r="A53" s="80" t="s">
         <v>103</v>
       </c>
@@ -20120,7 +20132,7 @@
         <v>7.8793892417766198</v>
       </c>
     </row>
-    <row r="54" spans="1:26" ht="15.75" thickBot="1">
+    <row r="54" spans="1:26" ht="15" thickBot="1">
       <c r="A54" s="80" t="s">
         <v>83</v>
       </c>
@@ -20168,7 +20180,7 @@
       </c>
       <c r="P54" s="87"/>
     </row>
-    <row r="55" spans="1:26" ht="15.75" thickBot="1">
+    <row r="55" spans="1:26" ht="15" thickBot="1">
       <c r="A55" s="80" t="s">
         <v>83</v>
       </c>
@@ -20255,7 +20267,7 @@
         <v>22.533930278145014</v>
       </c>
     </row>
-    <row r="56" spans="1:26" ht="15.75" thickBot="1">
+    <row r="56" spans="1:26" ht="15" thickBot="1">
       <c r="A56" s="80" t="s">
         <v>84</v>
       </c>
@@ -20302,7 +20314,7 @@
         <v>5.1162277320000005</v>
       </c>
     </row>
-    <row r="57" spans="1:26" ht="15.75" thickBot="1">
+    <row r="57" spans="1:26" ht="15" thickBot="1">
       <c r="A57" s="80" t="s">
         <v>84</v>
       </c>
@@ -20404,9 +20416,9 @@
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="23"/>
+    <col min="1" max="16384" width="9.109375" style="23"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -20516,35 +20528,35 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77FF3EF7-2BA1-4958-B9C1-EB66FD6DB01F}">
   <sheetPr codeName="Sheet15"/>
   <dimension ref="A3:AD37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
-    <col min="3" max="3" width="3.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.109375" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" customWidth="1"/>
+    <col min="3" max="3" width="3.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="5.6640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="6" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="5" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="7.5703125" customWidth="1"/>
-    <col min="25" max="25" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.5546875" customWidth="1"/>
+    <col min="25" max="25" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="26" max="28" width="6" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="6.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:30">
@@ -21015,7 +21027,7 @@
         <v>IE-MN</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="15.75" thickBot="1">
+    <row r="10" spans="1:30" ht="15" thickBot="1">
       <c r="A10" s="229" t="s">
         <v>279</v>
       </c>
@@ -21257,7 +21269,7 @@
                   </from>
                   <to>
                     <xdr:col>1</xdr:col>
-                    <xdr:colOff>28575</xdr:colOff>
+                    <xdr:colOff>30480</xdr:colOff>
                     <xdr:row>3</xdr:row>
                     <xdr:rowOff>0</xdr:rowOff>
                   </to>
@@ -21278,46 +21290,46 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1:AQ40"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="38.140625" style="133" customWidth="1"/>
+    <col min="1" max="1" width="38.109375" style="133" customWidth="1"/>
     <col min="2" max="2" width="13" style="131" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="7.5703125" style="134" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.140625" style="134"/>
-    <col min="6" max="6" width="6.140625" style="135" customWidth="1"/>
-    <col min="7" max="7" width="5.85546875" style="135" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.28515625" style="134" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.140625" style="135" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="7.5546875" style="134" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" style="134"/>
+    <col min="6" max="6" width="6.109375" style="135" customWidth="1"/>
+    <col min="7" max="7" width="5.88671875" style="135" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.33203125" style="134" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.109375" style="135" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6" style="135" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.85546875" style="135" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" style="132" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.140625" style="131" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.140625" style="131" customWidth="1"/>
-    <col min="15" max="15" width="5.28515625" style="131" customWidth="1"/>
-    <col min="16" max="16" width="7.28515625" style="131" customWidth="1"/>
-    <col min="17" max="17" width="7.28515625" style="131" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.140625" style="131" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="7.28515625" style="131" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.28515625" style="131" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.85546875" style="131" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="5.28515625" style="131" customWidth="1"/>
-    <col min="26" max="26" width="5.28515625" style="135" customWidth="1"/>
-    <col min="27" max="27" width="8.140625" style="132" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.7109375" style="132" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="5.5703125" style="131" customWidth="1"/>
-    <col min="31" max="31" width="8.7109375" style="131" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="8.7109375" style="131" customWidth="1"/>
-    <col min="33" max="33" width="5.5703125" style="131" customWidth="1"/>
-    <col min="34" max="34" width="5.85546875" style="131" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.88671875" style="135" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.6640625" style="132" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.109375" style="131" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.109375" style="131" customWidth="1"/>
+    <col min="15" max="15" width="5.33203125" style="131" customWidth="1"/>
+    <col min="16" max="16" width="7.33203125" style="131" customWidth="1"/>
+    <col min="17" max="17" width="7.33203125" style="131" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.109375" style="131" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="7.33203125" style="131" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.33203125" style="131" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.88671875" style="131" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="5.33203125" style="131" customWidth="1"/>
+    <col min="26" max="26" width="5.33203125" style="135" customWidth="1"/>
+    <col min="27" max="27" width="8.109375" style="132" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.6640625" style="132" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="5.5546875" style="131" customWidth="1"/>
+    <col min="31" max="31" width="8.6640625" style="131" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="8.6640625" style="131" customWidth="1"/>
+    <col min="33" max="33" width="5.5546875" style="131" customWidth="1"/>
+    <col min="34" max="34" width="5.88671875" style="131" bestFit="1" customWidth="1"/>
     <col min="35" max="36" width="7" style="131" customWidth="1"/>
-    <col min="37" max="40" width="5.5703125" style="131" customWidth="1"/>
-    <col min="41" max="41" width="8.7109375" style="132" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="4.28515625" style="132" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="9.28515625" style="131" bestFit="1" customWidth="1"/>
-    <col min="44" max="16384" width="9.140625" style="131"/>
+    <col min="37" max="40" width="5.5546875" style="131" customWidth="1"/>
+    <col min="41" max="41" width="8.6640625" style="132" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="4.33203125" style="132" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="9.33203125" style="131" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.109375" style="131"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="111.75" thickBot="1">
+    <row r="1" spans="1:43" ht="121.2" thickBot="1">
       <c r="A1" s="212" t="s">
         <v>428</v>
       </c>
@@ -21820,7 +21832,7 @@
         <v>172.71258946798309</v>
       </c>
     </row>
-    <row r="6" spans="1:43" ht="13.5" thickBot="1">
+    <row r="6" spans="1:43" ht="13.8" thickBot="1">
       <c r="A6" s="322" t="s">
         <v>197</v>
       </c>
@@ -22098,7 +22110,7 @@
         <v>14978.040387890453</v>
       </c>
     </row>
-    <row r="8" spans="1:43" ht="13.5" thickBot="1">
+    <row r="8" spans="1:43" ht="13.8" thickBot="1">
       <c r="A8" s="344" t="s">
         <v>199</v>
       </c>
@@ -23556,7 +23568,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:43" ht="13.5" thickBot="1">
+    <row r="24" spans="1:43" ht="13.8" thickBot="1">
       <c r="A24" s="322" t="s">
         <v>618</v>
       </c>
@@ -23636,7 +23648,7 @@
         <v>-2.4439547706873483</v>
       </c>
     </row>
-    <row r="25" spans="1:43" ht="13.5" thickBot="1">
+    <row r="25" spans="1:43" ht="13.8" thickBot="1">
       <c r="A25" s="383" t="s">
         <v>205</v>
       </c>
@@ -23712,7 +23724,7 @@
         <v>425.56331988324462</v>
       </c>
     </row>
-    <row r="26" spans="1:43" ht="13.5" thickBot="1">
+    <row r="26" spans="1:43" ht="13.8" thickBot="1">
       <c r="A26" s="427" t="s">
         <v>206</v>
       </c>
@@ -23903,37 +23915,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E428973-03EE-47B5-B88E-68B51CDC4391}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B3:AC86"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="1.5703125" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="46.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="1.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.85546875" customWidth="1"/>
-    <col min="6" max="6" width="85.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" customWidth="1"/>
-    <col min="8" max="8" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="1.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="35.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="1.5703125" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.5546875" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="46.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="1.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.88671875" customWidth="1"/>
+    <col min="6" max="6" width="85.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="1.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="27.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="1.5546875" customWidth="1"/>
+    <col min="16" max="16" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="20" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="1.5703125" customWidth="1"/>
-    <col min="20" max="20" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="1.5703125" customWidth="1"/>
-    <col min="22" max="22" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="26.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="1.5703125" customWidth="1"/>
-    <col min="26" max="26" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="1.5703125" customWidth="1"/>
-    <col min="29" max="29" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="1.5546875" customWidth="1"/>
+    <col min="20" max="20" width="18.109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="1.5546875" customWidth="1"/>
+    <col min="22" max="22" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="1.5546875" customWidth="1"/>
+    <col min="26" max="26" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="1.5546875" customWidth="1"/>
+    <col min="29" max="29" width="13.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:29" ht="18.75">
+    <row r="3" spans="2:29" ht="18">
       <c r="B3" s="165" t="s">
         <v>282</v>
       </c>
@@ -23962,7 +23974,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="4" spans="2:29" ht="15.75" thickBot="1">
+    <row r="4" spans="2:29" ht="15" thickBot="1">
       <c r="B4" s="166" t="s">
         <v>279</v>
       </c>
@@ -27017,12 +27029,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="B2:I77"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <dimension ref="B2:I79"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="49.85546875" customWidth="1"/>
+    <col min="3" max="3" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="49.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9">
@@ -27037,7 +27049,7 @@
       <c r="H2" s="170"/>
       <c r="I2" s="170"/>
     </row>
-    <row r="3" spans="2:9" ht="15.75" thickBot="1">
+    <row r="3" spans="2:9" ht="15" thickBot="1">
       <c r="B3" s="166" t="s">
         <v>15</v>
       </c>
@@ -28520,6 +28532,34 @@
       </c>
       <c r="E77" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="78" spans="2:9">
+      <c r="B78" s="174" t="s">
+        <v>270</v>
+      </c>
+      <c r="C78" t="s">
+        <v>665</v>
+      </c>
+      <c r="D78" t="s">
+        <v>667</v>
+      </c>
+      <c r="E78" s="174" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="79" spans="2:9">
+      <c r="B79" s="174" t="s">
+        <v>270</v>
+      </c>
+      <c r="C79" t="s">
+        <v>666</v>
+      </c>
+      <c r="D79" t="s">
+        <v>668</v>
+      </c>
+      <c r="E79" s="174" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -28532,23 +28572,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ABBFF4F-A0CF-43AC-AC4F-5B8E72D4ACA3}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="B1:T91"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" customWidth="1"/>
-    <col min="8" max="8" width="30.28515625" customWidth="1"/>
-    <col min="9" max="9" width="25.28515625" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" customWidth="1"/>
-    <col min="14" max="14" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.140625" customWidth="1"/>
+    <col min="5" max="5" width="58.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" customWidth="1"/>
+    <col min="7" max="7" width="12.88671875" customWidth="1"/>
+    <col min="8" max="8" width="30.33203125" customWidth="1"/>
+    <col min="9" max="9" width="25.33203125" customWidth="1"/>
+    <col min="10" max="10" width="17.33203125" customWidth="1"/>
+    <col min="14" max="14" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="26.25">
+    <row r="1" spans="2:10" ht="25.8">
       <c r="B1" s="175" t="s">
         <v>350</v>
       </c>
@@ -28574,7 +28614,7 @@
       <c r="I3" s="170"/>
       <c r="J3" s="170"/>
     </row>
-    <row r="4" spans="2:10" ht="15.75" thickBot="1">
+    <row r="4" spans="2:10" ht="15" thickBot="1">
       <c r="B4" s="166" t="s">
         <v>1</v>
       </c>
@@ -30929,278 +30969,278 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FE4B577-4D89-4799-9E6A-0D10D8F4A4E3}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B1:S14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="23"/>
-    <col min="2" max="2" width="11.5703125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="23" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.109375" style="23"/>
+    <col min="2" max="2" width="11.5546875" style="23" customWidth="1"/>
+    <col min="3" max="3" width="11.33203125" style="23" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26" style="23" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="9.140625" style="23"/>
-    <col min="9" max="9" width="10.28515625" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.85546875" style="23" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" style="23"/>
-    <col min="13" max="13" width="11.28515625" style="23" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="9.109375" style="23"/>
+    <col min="9" max="9" width="10.33203125" style="23" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.88671875" style="23" customWidth="1"/>
+    <col min="12" max="12" width="9.109375" style="23"/>
+    <col min="13" max="13" width="11.33203125" style="23" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.6640625" style="23" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="37" style="23" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="9.85546875" style="23" customWidth="1"/>
-    <col min="18" max="262" width="9.140625" style="23"/>
-    <col min="263" max="263" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="264" max="264" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="265" max="265" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="266" max="518" width="9.140625" style="23"/>
-    <col min="519" max="519" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="520" max="520" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="521" max="521" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="522" max="774" width="9.140625" style="23"/>
-    <col min="775" max="775" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="776" max="776" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="777" max="777" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="778" max="1030" width="9.140625" style="23"/>
-    <col min="1031" max="1031" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="1032" max="1032" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="1033" max="1033" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="1034" max="1286" width="9.140625" style="23"/>
-    <col min="1287" max="1287" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="1288" max="1288" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="1289" max="1289" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="1290" max="1542" width="9.140625" style="23"/>
-    <col min="1543" max="1543" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="1544" max="1544" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="1545" max="1545" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="1546" max="1798" width="9.140625" style="23"/>
-    <col min="1799" max="1799" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="1800" max="1800" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="1801" max="1801" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="1802" max="2054" width="9.140625" style="23"/>
-    <col min="2055" max="2055" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="2056" max="2056" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="2057" max="2057" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="2058" max="2310" width="9.140625" style="23"/>
-    <col min="2311" max="2311" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="2312" max="2312" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="2313" max="2313" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="2314" max="2566" width="9.140625" style="23"/>
-    <col min="2567" max="2567" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="2568" max="2568" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="2569" max="2569" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="2570" max="2822" width="9.140625" style="23"/>
-    <col min="2823" max="2823" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="2824" max="2824" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="2825" max="2825" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="2826" max="3078" width="9.140625" style="23"/>
-    <col min="3079" max="3079" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="3080" max="3080" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="3081" max="3081" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="3082" max="3334" width="9.140625" style="23"/>
-    <col min="3335" max="3335" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="3336" max="3336" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="3337" max="3337" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="3338" max="3590" width="9.140625" style="23"/>
-    <col min="3591" max="3591" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="3592" max="3592" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="3593" max="3593" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="3594" max="3846" width="9.140625" style="23"/>
-    <col min="3847" max="3847" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="3848" max="3848" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="3849" max="3849" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="3850" max="4102" width="9.140625" style="23"/>
-    <col min="4103" max="4103" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="4104" max="4104" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="4105" max="4105" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="4106" max="4358" width="9.140625" style="23"/>
-    <col min="4359" max="4359" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="4360" max="4360" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="4361" max="4361" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="4362" max="4614" width="9.140625" style="23"/>
-    <col min="4615" max="4615" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="4616" max="4616" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="4617" max="4617" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="4618" max="4870" width="9.140625" style="23"/>
-    <col min="4871" max="4871" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="4872" max="4872" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="4873" max="4873" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="4874" max="5126" width="9.140625" style="23"/>
-    <col min="5127" max="5127" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="5128" max="5128" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="5129" max="5129" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="5130" max="5382" width="9.140625" style="23"/>
-    <col min="5383" max="5383" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="5384" max="5384" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="5385" max="5385" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="5386" max="5638" width="9.140625" style="23"/>
-    <col min="5639" max="5639" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="5640" max="5640" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="5641" max="5641" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="5642" max="5894" width="9.140625" style="23"/>
-    <col min="5895" max="5895" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="5896" max="5896" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="5897" max="5897" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="5898" max="6150" width="9.140625" style="23"/>
-    <col min="6151" max="6151" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="6152" max="6152" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="6153" max="6153" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="6154" max="6406" width="9.140625" style="23"/>
-    <col min="6407" max="6407" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="6408" max="6408" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="6409" max="6409" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="6410" max="6662" width="9.140625" style="23"/>
-    <col min="6663" max="6663" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="6664" max="6664" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="6665" max="6665" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="6666" max="6918" width="9.140625" style="23"/>
-    <col min="6919" max="6919" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="6920" max="6920" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="6921" max="6921" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="6922" max="7174" width="9.140625" style="23"/>
-    <col min="7175" max="7175" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="7176" max="7176" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="7177" max="7177" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="7178" max="7430" width="9.140625" style="23"/>
-    <col min="7431" max="7431" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="7432" max="7432" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="7433" max="7433" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="7434" max="7686" width="9.140625" style="23"/>
-    <col min="7687" max="7687" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="7688" max="7688" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="7689" max="7689" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="7690" max="7942" width="9.140625" style="23"/>
-    <col min="7943" max="7943" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="7944" max="7944" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="7945" max="7945" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="7946" max="8198" width="9.140625" style="23"/>
-    <col min="8199" max="8199" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="8200" max="8200" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="8201" max="8201" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="8202" max="8454" width="9.140625" style="23"/>
-    <col min="8455" max="8455" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="8456" max="8456" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="8457" max="8457" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="8458" max="8710" width="9.140625" style="23"/>
-    <col min="8711" max="8711" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="8712" max="8712" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="8713" max="8713" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="8714" max="8966" width="9.140625" style="23"/>
-    <col min="8967" max="8967" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="8968" max="8968" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="8969" max="8969" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="8970" max="9222" width="9.140625" style="23"/>
-    <col min="9223" max="9223" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="9224" max="9224" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="9225" max="9225" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="9226" max="9478" width="9.140625" style="23"/>
-    <col min="9479" max="9479" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="9480" max="9480" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="9481" max="9481" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="9482" max="9734" width="9.140625" style="23"/>
-    <col min="9735" max="9735" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="9736" max="9736" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="9737" max="9737" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="9738" max="9990" width="9.140625" style="23"/>
-    <col min="9991" max="9991" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="9992" max="9992" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="9993" max="9993" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="9994" max="10246" width="9.140625" style="23"/>
-    <col min="10247" max="10247" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="10248" max="10248" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="10249" max="10249" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="10250" max="10502" width="9.140625" style="23"/>
-    <col min="10503" max="10503" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="10504" max="10504" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="10505" max="10505" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="10506" max="10758" width="9.140625" style="23"/>
-    <col min="10759" max="10759" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="10760" max="10760" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="10761" max="10761" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="10762" max="11014" width="9.140625" style="23"/>
-    <col min="11015" max="11015" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="11016" max="11016" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="11017" max="11017" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="11018" max="11270" width="9.140625" style="23"/>
-    <col min="11271" max="11271" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="11272" max="11272" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="11273" max="11273" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="11274" max="11526" width="9.140625" style="23"/>
-    <col min="11527" max="11527" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="11528" max="11528" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="11529" max="11529" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="11530" max="11782" width="9.140625" style="23"/>
-    <col min="11783" max="11783" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="11784" max="11784" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="11785" max="11785" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="11786" max="12038" width="9.140625" style="23"/>
-    <col min="12039" max="12039" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="12040" max="12040" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="12041" max="12041" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="12042" max="12294" width="9.140625" style="23"/>
-    <col min="12295" max="12295" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="12296" max="12296" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="12297" max="12297" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="12298" max="12550" width="9.140625" style="23"/>
-    <col min="12551" max="12551" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="12552" max="12552" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="12553" max="12553" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="12554" max="12806" width="9.140625" style="23"/>
-    <col min="12807" max="12807" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="12808" max="12808" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="12809" max="12809" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="12810" max="13062" width="9.140625" style="23"/>
-    <col min="13063" max="13063" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="13064" max="13064" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="13065" max="13065" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="13066" max="13318" width="9.140625" style="23"/>
-    <col min="13319" max="13319" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="13320" max="13320" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="13321" max="13321" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="13322" max="13574" width="9.140625" style="23"/>
-    <col min="13575" max="13575" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="13576" max="13576" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="13577" max="13577" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="13578" max="13830" width="9.140625" style="23"/>
-    <col min="13831" max="13831" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="13832" max="13832" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="13833" max="13833" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="13834" max="14086" width="9.140625" style="23"/>
-    <col min="14087" max="14087" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="14088" max="14088" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="14089" max="14089" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="14090" max="14342" width="9.140625" style="23"/>
-    <col min="14343" max="14343" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="14344" max="14344" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="14345" max="14345" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="14346" max="14598" width="9.140625" style="23"/>
-    <col min="14599" max="14599" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="14600" max="14600" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="14601" max="14601" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="14602" max="14854" width="9.140625" style="23"/>
-    <col min="14855" max="14855" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="14856" max="14856" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="14857" max="14857" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="14858" max="15110" width="9.140625" style="23"/>
-    <col min="15111" max="15111" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="15112" max="15112" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="15113" max="15113" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="15114" max="15366" width="9.140625" style="23"/>
-    <col min="15367" max="15367" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="15368" max="15368" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="15369" max="15369" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="15370" max="15622" width="9.140625" style="23"/>
-    <col min="15623" max="15623" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="15624" max="15624" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="15625" max="15625" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="15626" max="15878" width="9.140625" style="23"/>
-    <col min="15879" max="15879" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="15880" max="15880" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="15881" max="15881" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="15882" max="16134" width="9.140625" style="23"/>
-    <col min="16135" max="16135" width="10.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="16136" max="16136" width="14.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="16137" max="16137" width="11.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="16138" max="16384" width="9.140625" style="23"/>
+    <col min="16" max="17" width="9.88671875" style="23" customWidth="1"/>
+    <col min="18" max="262" width="9.109375" style="23"/>
+    <col min="263" max="263" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="264" max="264" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="265" max="265" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="266" max="518" width="9.109375" style="23"/>
+    <col min="519" max="519" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="520" max="520" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="521" max="521" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="522" max="774" width="9.109375" style="23"/>
+    <col min="775" max="775" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="776" max="776" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="777" max="777" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="778" max="1030" width="9.109375" style="23"/>
+    <col min="1031" max="1031" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="1032" max="1032" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="1033" max="1033" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="1034" max="1286" width="9.109375" style="23"/>
+    <col min="1287" max="1287" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="1288" max="1288" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="1289" max="1289" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="1290" max="1542" width="9.109375" style="23"/>
+    <col min="1543" max="1543" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="1544" max="1544" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="1545" max="1545" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="1546" max="1798" width="9.109375" style="23"/>
+    <col min="1799" max="1799" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="1800" max="1800" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="1801" max="1801" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="1802" max="2054" width="9.109375" style="23"/>
+    <col min="2055" max="2055" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="2056" max="2056" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="2057" max="2057" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="2058" max="2310" width="9.109375" style="23"/>
+    <col min="2311" max="2311" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="2312" max="2312" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="2313" max="2313" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="2314" max="2566" width="9.109375" style="23"/>
+    <col min="2567" max="2567" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="2568" max="2568" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="2569" max="2569" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="2570" max="2822" width="9.109375" style="23"/>
+    <col min="2823" max="2823" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="2824" max="2824" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="2825" max="2825" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="2826" max="3078" width="9.109375" style="23"/>
+    <col min="3079" max="3079" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="3080" max="3080" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="3081" max="3081" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="3082" max="3334" width="9.109375" style="23"/>
+    <col min="3335" max="3335" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="3336" max="3336" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="3337" max="3337" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="3338" max="3590" width="9.109375" style="23"/>
+    <col min="3591" max="3591" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="3592" max="3592" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="3593" max="3593" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="3594" max="3846" width="9.109375" style="23"/>
+    <col min="3847" max="3847" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="3848" max="3848" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="3849" max="3849" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="3850" max="4102" width="9.109375" style="23"/>
+    <col min="4103" max="4103" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="4104" max="4104" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="4105" max="4105" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="4106" max="4358" width="9.109375" style="23"/>
+    <col min="4359" max="4359" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="4360" max="4360" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="4361" max="4361" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="4362" max="4614" width="9.109375" style="23"/>
+    <col min="4615" max="4615" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="4616" max="4616" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="4617" max="4617" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="4618" max="4870" width="9.109375" style="23"/>
+    <col min="4871" max="4871" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="4872" max="4872" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="4873" max="4873" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="4874" max="5126" width="9.109375" style="23"/>
+    <col min="5127" max="5127" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="5128" max="5128" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="5129" max="5129" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="5130" max="5382" width="9.109375" style="23"/>
+    <col min="5383" max="5383" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="5384" max="5384" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="5385" max="5385" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="5386" max="5638" width="9.109375" style="23"/>
+    <col min="5639" max="5639" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="5640" max="5640" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="5641" max="5641" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="5642" max="5894" width="9.109375" style="23"/>
+    <col min="5895" max="5895" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="5896" max="5896" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="5897" max="5897" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="5898" max="6150" width="9.109375" style="23"/>
+    <col min="6151" max="6151" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="6152" max="6152" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="6153" max="6153" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="6154" max="6406" width="9.109375" style="23"/>
+    <col min="6407" max="6407" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="6408" max="6408" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="6409" max="6409" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="6410" max="6662" width="9.109375" style="23"/>
+    <col min="6663" max="6663" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="6664" max="6664" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="6665" max="6665" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="6666" max="6918" width="9.109375" style="23"/>
+    <col min="6919" max="6919" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="6920" max="6920" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="6921" max="6921" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="6922" max="7174" width="9.109375" style="23"/>
+    <col min="7175" max="7175" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="7176" max="7176" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="7177" max="7177" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="7178" max="7430" width="9.109375" style="23"/>
+    <col min="7431" max="7431" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="7432" max="7432" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="7433" max="7433" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="7434" max="7686" width="9.109375" style="23"/>
+    <col min="7687" max="7687" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="7688" max="7688" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="7689" max="7689" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="7690" max="7942" width="9.109375" style="23"/>
+    <col min="7943" max="7943" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="7944" max="7944" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="7945" max="7945" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="7946" max="8198" width="9.109375" style="23"/>
+    <col min="8199" max="8199" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="8200" max="8200" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="8201" max="8201" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="8202" max="8454" width="9.109375" style="23"/>
+    <col min="8455" max="8455" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="8456" max="8456" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="8457" max="8457" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="8458" max="8710" width="9.109375" style="23"/>
+    <col min="8711" max="8711" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="8712" max="8712" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="8713" max="8713" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="8714" max="8966" width="9.109375" style="23"/>
+    <col min="8967" max="8967" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="8968" max="8968" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="8969" max="8969" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="8970" max="9222" width="9.109375" style="23"/>
+    <col min="9223" max="9223" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="9224" max="9224" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="9225" max="9225" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="9226" max="9478" width="9.109375" style="23"/>
+    <col min="9479" max="9479" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="9480" max="9480" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="9481" max="9481" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="9482" max="9734" width="9.109375" style="23"/>
+    <col min="9735" max="9735" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="9736" max="9736" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="9737" max="9737" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="9738" max="9990" width="9.109375" style="23"/>
+    <col min="9991" max="9991" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="9992" max="9992" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="9993" max="9993" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="9994" max="10246" width="9.109375" style="23"/>
+    <col min="10247" max="10247" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="10248" max="10248" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="10249" max="10249" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="10250" max="10502" width="9.109375" style="23"/>
+    <col min="10503" max="10503" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="10504" max="10504" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="10505" max="10505" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="10506" max="10758" width="9.109375" style="23"/>
+    <col min="10759" max="10759" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="10760" max="10760" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="10761" max="10761" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="10762" max="11014" width="9.109375" style="23"/>
+    <col min="11015" max="11015" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="11016" max="11016" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="11017" max="11017" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="11018" max="11270" width="9.109375" style="23"/>
+    <col min="11271" max="11271" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="11272" max="11272" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="11273" max="11273" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="11274" max="11526" width="9.109375" style="23"/>
+    <col min="11527" max="11527" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="11528" max="11528" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="11529" max="11529" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="11530" max="11782" width="9.109375" style="23"/>
+    <col min="11783" max="11783" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="11784" max="11784" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="11785" max="11785" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="11786" max="12038" width="9.109375" style="23"/>
+    <col min="12039" max="12039" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="12040" max="12040" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="12041" max="12041" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="12042" max="12294" width="9.109375" style="23"/>
+    <col min="12295" max="12295" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="12296" max="12296" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="12297" max="12297" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="12298" max="12550" width="9.109375" style="23"/>
+    <col min="12551" max="12551" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="12552" max="12552" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="12553" max="12553" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="12554" max="12806" width="9.109375" style="23"/>
+    <col min="12807" max="12807" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="12808" max="12808" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="12809" max="12809" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="12810" max="13062" width="9.109375" style="23"/>
+    <col min="13063" max="13063" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="13064" max="13064" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="13065" max="13065" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="13066" max="13318" width="9.109375" style="23"/>
+    <col min="13319" max="13319" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="13320" max="13320" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="13321" max="13321" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="13322" max="13574" width="9.109375" style="23"/>
+    <col min="13575" max="13575" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="13576" max="13576" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="13577" max="13577" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="13578" max="13830" width="9.109375" style="23"/>
+    <col min="13831" max="13831" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="13832" max="13832" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="13833" max="13833" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="13834" max="14086" width="9.109375" style="23"/>
+    <col min="14087" max="14087" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="14088" max="14088" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="14089" max="14089" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="14090" max="14342" width="9.109375" style="23"/>
+    <col min="14343" max="14343" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="14344" max="14344" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="14345" max="14345" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="14346" max="14598" width="9.109375" style="23"/>
+    <col min="14599" max="14599" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="14600" max="14600" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="14601" max="14601" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="14602" max="14854" width="9.109375" style="23"/>
+    <col min="14855" max="14855" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="14856" max="14856" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="14857" max="14857" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="14858" max="15110" width="9.109375" style="23"/>
+    <col min="15111" max="15111" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="15112" max="15112" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="15113" max="15113" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="15114" max="15366" width="9.109375" style="23"/>
+    <col min="15367" max="15367" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="15368" max="15368" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="15369" max="15369" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="15370" max="15622" width="9.109375" style="23"/>
+    <col min="15623" max="15623" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="15624" max="15624" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="15625" max="15625" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="15626" max="15878" width="9.109375" style="23"/>
+    <col min="15879" max="15879" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="15880" max="15880" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="15881" max="15881" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="15882" max="16134" width="9.109375" style="23"/>
+    <col min="16135" max="16135" width="10.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="16136" max="16136" width="14.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="16137" max="16137" width="11.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="16138" max="16384" width="9.109375" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:19" ht="18.75">
+    <row r="1" spans="2:19" ht="18">
       <c r="B1" s="154" t="s">
         <v>224</v>
       </c>
@@ -31247,7 +31287,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="5" spans="2:19" ht="15.75" thickBot="1">
+    <row r="5" spans="2:19" ht="15" thickBot="1">
       <c r="B5" s="159" t="s">
         <v>211</v>
       </c>
@@ -31456,37 +31496,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B1:U69"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="23"/>
-    <col min="2" max="2" width="12.5703125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="23.28515625" style="23" customWidth="1"/>
-    <col min="4" max="4" width="21.28515625" style="23" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.85546875" style="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13.28515625" style="23" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" style="23" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.28515625" style="23" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.140625" style="23" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" style="23" customWidth="1"/>
-    <col min="13" max="13" width="19.140625" style="23" customWidth="1"/>
-    <col min="14" max="14" width="15.140625" style="23" customWidth="1"/>
-    <col min="15" max="15" width="10.5703125" style="23" customWidth="1"/>
-    <col min="16" max="22" width="9.140625" style="23"/>
+    <col min="1" max="1" width="9.109375" style="23"/>
+    <col min="2" max="2" width="12.5546875" style="23" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" style="23" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" style="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.88671875" style="23" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13.33203125" style="23" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.33203125" style="23" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.109375" style="23" customWidth="1"/>
+    <col min="12" max="12" width="12.6640625" style="23" customWidth="1"/>
+    <col min="13" max="13" width="19.109375" style="23" customWidth="1"/>
+    <col min="14" max="14" width="15.109375" style="23" customWidth="1"/>
+    <col min="15" max="15" width="10.5546875" style="23" customWidth="1"/>
+    <col min="16" max="22" width="9.109375" style="23"/>
     <col min="23" max="23" width="16" style="23" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="19.28515625" style="23" customWidth="1"/>
-    <col min="25" max="25" width="38.5703125" style="23" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="23"/>
+    <col min="24" max="24" width="19.33203125" style="23" customWidth="1"/>
+    <col min="25" max="25" width="38.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.109375" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:20" ht="18.75">
+    <row r="1" spans="2:20" ht="18">
       <c r="B1" s="3" t="s">
         <v>544</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
     </row>
-    <row r="3" spans="2:20" ht="18.75">
+    <row r="3" spans="2:20" ht="18">
       <c r="G3" s="257" t="s">
         <v>557</v>
       </c>
@@ -31540,7 +31580,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="2:20" ht="26.25" thickBot="1">
+    <row r="5" spans="2:20" ht="28.2" thickBot="1">
       <c r="C5" s="9" t="s">
         <v>515</v>
       </c>
@@ -33853,16 +33893,16 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A665F926-DECD-4DB2-B495-3F9BFC1DFD4C}">
   <dimension ref="B2:J18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="19.85546875" customWidth="1"/>
-    <col min="4" max="4" width="26.85546875" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="19.88671875" customWidth="1"/>
+    <col min="4" max="4" width="26.88671875" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.28515625" customWidth="1"/>
+    <col min="7" max="7" width="18.6640625" customWidth="1"/>
+    <col min="9" max="9" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10">
@@ -33878,7 +33918,7 @@
       <c r="I2" s="170"/>
       <c r="J2" s="170"/>
     </row>
-    <row r="3" spans="2:10" ht="15.75" thickBot="1">
+    <row r="3" spans="2:10" ht="15" thickBot="1">
       <c r="B3" s="166" t="s">
         <v>1</v>
       </c>
@@ -33907,7 +33947,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:10" ht="51">
+    <row r="4" spans="2:10" ht="55.2">
       <c r="B4" s="172" t="s">
         <v>133</v>
       </c>
@@ -33964,7 +34004,7 @@
       </c>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="2:10" ht="15.75" thickBot="1">
+    <row r="10" spans="2:10" ht="15" thickBot="1">
       <c r="B10" s="166" t="s">
         <v>513</v>
       </c>
@@ -34079,6 +34119,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010087B74FDAF7A4FB4D876E5EA45926113E" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="327522a6d5518d67d5f1063e9cc64cf0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3a32fc56-8470-4d77-ad86-bef2a7229878" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ffd5532d255be23b9fb13183c07e1fd0" ns2:_="">
     <xsd:import namespace="3a32fc56-8470-4d77-ad86-bef2a7229878"/>
@@ -34224,22 +34279,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1EBC224-6025-40B6-954C-A60FF473B45B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="3a32fc56-8470-4d77-ad86-bef2a7229878"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44F399E6-2CA4-4BC3-AE7C-3570BA9F00A0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F32A5943-069C-47E6-B7B1-1C4E8CC11B6B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34255,28 +34319,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44F399E6-2CA4-4BC3-AE7C-3570BA9F00A0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1EBC224-6025-40B6-954C-A60FF473B45B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="3a32fc56-8470-4d77-ad86-bef2a7229878"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/VT_IE_SUP.xlsx
+++ b/VT_IE_SUP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\BSuleimenov\Documents\GitHub\times-ireland-model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C979EF9-666E-4C1B-8283-003E80B0B879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72702898-E314-4884-A122-7BD141888B8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="7" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="23" r:id="rId1"/>
@@ -5648,7 +5648,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="484">
+  <cellXfs count="486">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="2" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -6966,6 +6966,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -16204,7 +16210,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet10"/>
-  <dimension ref="B2:T36"/>
+  <dimension ref="B2:T37"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9.109375" style="23"/>
@@ -16359,23 +16365,23 @@
         <v>31.536000000000001</v>
       </c>
       <c r="K5" s="41">
-        <f>G22</f>
+        <f>G23</f>
         <v>12.775231427006712</v>
       </c>
       <c r="L5" s="41">
-        <f>H22</f>
+        <f>H23</f>
         <v>13.844655136887908</v>
       </c>
       <c r="M5" s="41">
-        <f>I22</f>
+        <f>I23</f>
         <v>20.699646648446279</v>
       </c>
       <c r="N5" s="41">
-        <f>J22</f>
+        <f>J23</f>
         <v>24.100186765447592</v>
       </c>
       <c r="O5" s="41">
-        <f>K22</f>
+        <f>K23</f>
         <v>27.970361406895258</v>
       </c>
       <c r="P5" s="437">
@@ -16418,24 +16424,24 @@
         <v>31.536000000000001</v>
       </c>
       <c r="K6" s="28">
-        <f>K5*0.7</f>
-        <v>8.9426619989046987</v>
+        <f>K5*0.5</f>
+        <v>6.3876157135033562</v>
       </c>
       <c r="L6" s="28">
-        <f>L5*0.7</f>
-        <v>9.6912585958215356</v>
+        <f t="shared" ref="L6:O6" si="1">L5*0.5</f>
+        <v>6.9223275684439542</v>
       </c>
       <c r="M6" s="28">
-        <f>M5*0.7</f>
-        <v>14.489752653912394</v>
+        <f t="shared" si="1"/>
+        <v>10.34982332422314</v>
       </c>
       <c r="N6" s="28">
-        <f>N5*0.7</f>
-        <v>16.870130735813312</v>
+        <f t="shared" si="1"/>
+        <v>12.050093382723796</v>
       </c>
       <c r="O6" s="28">
-        <f>O5*0.7</f>
-        <v>19.579252984826677</v>
+        <f t="shared" si="1"/>
+        <v>13.985180703447629</v>
       </c>
       <c r="P6" s="438">
         <v>0</v>
@@ -16446,122 +16452,116 @@
       <c r="R6"/>
     </row>
     <row r="7" spans="2:20">
-      <c r="B7" s="29" t="s">
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="484"/>
+      <c r="O7" s="484"/>
+      <c r="P7" s="485"/>
+      <c r="Q7" s="485"/>
+      <c r="R7"/>
+    </row>
+    <row r="8" spans="2:20">
+      <c r="B8" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="478" t="s">
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="478" t="s">
         <v>159</v>
       </c>
-      <c r="H7" s="478"/>
-      <c r="I7" s="478"/>
-      <c r="J7" s="478"/>
-      <c r="K7" s="478"/>
-      <c r="L7" s="193" t="s">
+      <c r="H8" s="478"/>
+      <c r="I8" s="478"/>
+      <c r="J8" s="478"/>
+      <c r="K8" s="478"/>
+      <c r="L8" s="193" t="s">
         <v>67</v>
       </c>
-      <c r="M7" s="192"/>
-      <c r="N7" s="482" t="s">
+      <c r="M8" s="192"/>
+      <c r="N8" s="482" t="s">
         <v>220</v>
       </c>
-      <c r="O7" s="482"/>
-      <c r="P7"/>
-      <c r="Q7"/>
-      <c r="R7"/>
-    </row>
-    <row r="9" spans="2:20">
-      <c r="O9" s="26"/>
-      <c r="P9" s="26"/>
-      <c r="Q9" s="26"/>
-    </row>
-    <row r="11" spans="2:20">
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="E11"/>
-      <c r="F11"/>
-      <c r="G11"/>
-      <c r="H11"/>
-      <c r="I11"/>
-      <c r="J11"/>
-      <c r="K11"/>
-      <c r="L11"/>
-      <c r="M11">
-        <f>H5*8760*3.6</f>
-        <v>15768</v>
-      </c>
-      <c r="N11"/>
-      <c r="O11"/>
-      <c r="P11"/>
-      <c r="Q11"/>
-      <c r="R11"/>
-      <c r="S11"/>
-      <c r="T11"/>
+      <c r="O8" s="482"/>
+      <c r="P8"/>
+      <c r="Q8"/>
+      <c r="R8"/>
+    </row>
+    <row r="10" spans="2:20">
+      <c r="O10" s="26"/>
+      <c r="P10" s="26"/>
+      <c r="Q10" s="26"/>
     </row>
     <row r="12" spans="2:20">
       <c r="C12"/>
-      <c r="E12" t="s">
-        <v>129</v>
-      </c>
+      <c r="D12"/>
+      <c r="E12"/>
       <c r="F12"/>
-      <c r="G12" t="s">
-        <v>128</v>
-      </c>
+      <c r="G12"/>
       <c r="H12"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
       <c r="L12"/>
-      <c r="M12"/>
+      <c r="M12">
+        <f>H5*8760*3.6</f>
+        <v>15768</v>
+      </c>
       <c r="N12"/>
       <c r="O12"/>
       <c r="P12"/>
       <c r="Q12"/>
       <c r="R12"/>
       <c r="S12"/>
+      <c r="T12"/>
     </row>
     <row r="13" spans="2:20">
       <c r="C13"/>
       <c r="E13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F13"/>
-      <c r="G13">
-        <v>2015</v>
-      </c>
-      <c r="H13">
-        <v>2020</v>
-      </c>
-      <c r="I13">
-        <v>2030</v>
-      </c>
-      <c r="J13">
-        <v>2040</v>
-      </c>
-      <c r="K13">
-        <v>2050</v>
-      </c>
+      <c r="G13" t="s">
+        <v>128</v>
+      </c>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13"/>
       <c r="L13"/>
       <c r="M13"/>
       <c r="N13"/>
       <c r="O13"/>
       <c r="P13"/>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
     </row>
     <row r="14" spans="2:20">
-      <c r="C14" t="s">
-        <v>126</v>
-      </c>
-      <c r="E14">
-        <v>1800</v>
+      <c r="C14"/>
+      <c r="E14" t="s">
+        <v>127</v>
       </c>
       <c r="F14"/>
-      <c r="G14"/>
-      <c r="H14"/>
-      <c r="I14"/>
-      <c r="J14"/>
-      <c r="K14"/>
+      <c r="G14">
+        <v>2015</v>
+      </c>
+      <c r="H14">
+        <v>2020</v>
+      </c>
+      <c r="I14">
+        <v>2030</v>
+      </c>
+      <c r="J14">
+        <v>2040</v>
+      </c>
+      <c r="K14">
+        <v>2050</v>
+      </c>
       <c r="L14"/>
       <c r="M14"/>
       <c r="N14"/>
@@ -16570,211 +16570,214 @@
     </row>
     <row r="15" spans="2:20">
       <c r="C15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E15">
-        <v>0.47499999999999998</v>
+        <v>1800</v>
       </c>
       <c r="F15"/>
-      <c r="G15" s="101">
-        <f>G19/$E$15</f>
-        <v>59.752421052631576</v>
-      </c>
-      <c r="H15" s="101">
-        <f>H19/$E$15</f>
-        <v>59.752421052631576</v>
-      </c>
-      <c r="I15" s="101">
-        <v>60</v>
-      </c>
-      <c r="J15" s="101">
-        <v>60</v>
-      </c>
-      <c r="K15" s="101">
-        <f>K19/$E$15</f>
-        <v>59.752421052631576</v>
-      </c>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
       <c r="L15"/>
-      <c r="M15" t="s">
-        <v>10</v>
-      </c>
-      <c r="N15" t="s">
-        <v>124</v>
-      </c>
+      <c r="M15"/>
+      <c r="N15"/>
       <c r="O15"/>
       <c r="P15"/>
     </row>
     <row r="16" spans="2:20">
-      <c r="C16"/>
-      <c r="E16"/>
+      <c r="C16" t="s">
+        <v>125</v>
+      </c>
+      <c r="E16">
+        <v>0.47499999999999998</v>
+      </c>
       <c r="F16"/>
-      <c r="G16"/>
-      <c r="H16"/>
-      <c r="I16"/>
-      <c r="J16"/>
-      <c r="K16"/>
+      <c r="G16" s="101">
+        <f>G20/$E$16</f>
+        <v>59.752421052631576</v>
+      </c>
+      <c r="H16" s="101">
+        <f>H20/$E$16</f>
+        <v>59.752421052631576</v>
+      </c>
+      <c r="I16" s="101">
+        <v>60</v>
+      </c>
+      <c r="J16" s="101">
+        <v>60</v>
+      </c>
+      <c r="K16" s="101">
+        <f>K20/$E$16</f>
+        <v>59.752421052631576</v>
+      </c>
       <c r="L16"/>
-      <c r="M16"/>
-      <c r="N16"/>
+      <c r="M16" t="s">
+        <v>10</v>
+      </c>
+      <c r="N16" t="s">
+        <v>124</v>
+      </c>
       <c r="O16"/>
       <c r="P16"/>
     </row>
     <row r="17" spans="3:20">
-      <c r="C17" t="s">
-        <v>123</v>
-      </c>
+      <c r="C17"/>
       <c r="E17"/>
       <c r="F17"/>
-      <c r="G17" s="87">
-        <f>Imports_Fossil!I7</f>
-        <v>5.672401594494854</v>
-      </c>
-      <c r="H17" s="87">
-        <f>Imports_Fossil!J7</f>
-        <v>6.1803778566884233</v>
-      </c>
-      <c r="I17" s="87">
-        <f>Imports_Fossil!K7</f>
-        <v>9.3975608505810264</v>
-      </c>
-      <c r="J17" s="87">
-        <f>Imports_Fossil!L7</f>
-        <v>11.006152347527328</v>
-      </c>
-      <c r="K17" s="87">
-        <f>Imports_Fossil!M7</f>
-        <v>12.890088334941915</v>
-      </c>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17"/>
+      <c r="K17"/>
       <c r="L17"/>
-      <c r="M17" s="100" t="str">
-        <f>Imports_Fossil!N7</f>
-        <v>WEO2019, WEO2020</v>
-      </c>
+      <c r="M17"/>
       <c r="N17"/>
       <c r="O17"/>
       <c r="P17"/>
     </row>
     <row r="18" spans="3:20">
-      <c r="C18"/>
+      <c r="C18" t="s">
+        <v>123</v>
+      </c>
       <c r="E18"/>
       <c r="F18"/>
-      <c r="G18" s="99">
-        <f>G17*G15/G19</f>
-        <v>11.941898093673379</v>
-      </c>
-      <c r="H18" s="99">
-        <f>H17*H15/H19</f>
-        <v>13.011321803554575</v>
-      </c>
-      <c r="I18" s="99">
-        <f t="shared" ref="I18:K18" si="1">I17*I15/I19</f>
-        <v>19.866313315112947</v>
-      </c>
-      <c r="J18" s="99">
-        <f t="shared" si="1"/>
-        <v>23.26685343211426</v>
-      </c>
-      <c r="K18" s="99">
-        <f t="shared" si="1"/>
-        <v>27.137028073561925</v>
+      <c r="G18" s="87">
+        <f>Imports_Fossil!I7</f>
+        <v>5.672401594494854</v>
+      </c>
+      <c r="H18" s="87">
+        <f>Imports_Fossil!J7</f>
+        <v>6.1803778566884233</v>
+      </c>
+      <c r="I18" s="87">
+        <f>Imports_Fossil!K7</f>
+        <v>9.3975608505810264</v>
+      </c>
+      <c r="J18" s="87">
+        <f>Imports_Fossil!L7</f>
+        <v>11.006152347527328</v>
+      </c>
+      <c r="K18" s="87">
+        <f>Imports_Fossil!M7</f>
+        <v>12.890088334941915</v>
       </c>
       <c r="L18"/>
-      <c r="M18" t="s">
-        <v>130</v>
+      <c r="M18" s="100" t="str">
+        <f>Imports_Fossil!N7</f>
+        <v>WEO2019, WEO2020</v>
       </c>
       <c r="N18"/>
       <c r="O18"/>
       <c r="P18"/>
     </row>
     <row r="19" spans="3:20">
-      <c r="C19" t="s">
-        <v>122</v>
-      </c>
-      <c r="E19">
-        <v>900</v>
-      </c>
+      <c r="C19"/>
+      <c r="E19"/>
       <c r="F19"/>
-      <c r="G19" s="87">
-        <f t="shared" ref="G19:K19" si="2">$E$19*8760*3.6*10^-6</f>
-        <v>28.382399999999997</v>
-      </c>
-      <c r="H19" s="87">
+      <c r="G19" s="99">
+        <f>G18*G16/G20</f>
+        <v>11.941898093673379</v>
+      </c>
+      <c r="H19" s="99">
+        <f>H18*H16/H20</f>
+        <v>13.011321803554575</v>
+      </c>
+      <c r="I19" s="99">
+        <f t="shared" ref="I19:K19" si="2">I18*I16/I20</f>
+        <v>19.866313315112947</v>
+      </c>
+      <c r="J19" s="99">
         <f t="shared" si="2"/>
-        <v>28.382399999999997</v>
-      </c>
-      <c r="I19" s="87">
+        <v>23.26685343211426</v>
+      </c>
+      <c r="K19" s="99">
         <f t="shared" si="2"/>
-        <v>28.382399999999997</v>
-      </c>
-      <c r="J19" s="87">
-        <f t="shared" si="2"/>
-        <v>28.382399999999997</v>
-      </c>
-      <c r="K19" s="87">
-        <f t="shared" si="2"/>
-        <v>28.382399999999997</v>
+        <v>27.137028073561925</v>
       </c>
       <c r="L19"/>
       <c r="M19" t="s">
-        <v>10</v>
-      </c>
-      <c r="N19" t="s">
-        <v>121</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="N19"/>
       <c r="O19"/>
       <c r="P19"/>
     </row>
     <row r="20" spans="3:20">
       <c r="C20" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>900</v>
       </c>
       <c r="F20"/>
-      <c r="G20" s="26">
-        <f t="shared" ref="G20:K20" si="3">$E$20/3.6</f>
-        <v>0.83333333333333326</v>
-      </c>
-      <c r="H20" s="26">
+      <c r="G20" s="87">
+        <f t="shared" ref="G20:K20" si="3">$E$20*8760*3.6*10^-6</f>
+        <v>28.382399999999997</v>
+      </c>
+      <c r="H20" s="87">
         <f t="shared" si="3"/>
-        <v>0.83333333333333326</v>
-      </c>
-      <c r="I20" s="26">
+        <v>28.382399999999997</v>
+      </c>
+      <c r="I20" s="87">
         <f t="shared" si="3"/>
-        <v>0.83333333333333326</v>
-      </c>
-      <c r="J20" s="26">
+        <v>28.382399999999997</v>
+      </c>
+      <c r="J20" s="87">
         <f t="shared" si="3"/>
-        <v>0.83333333333333326</v>
-      </c>
-      <c r="K20" s="26">
+        <v>28.382399999999997</v>
+      </c>
+      <c r="K20" s="87">
         <f t="shared" si="3"/>
-        <v>0.83333333333333326</v>
+        <v>28.382399999999997</v>
       </c>
       <c r="L20"/>
       <c r="M20" t="s">
-        <v>119</v>
+        <v>10</v>
       </c>
       <c r="N20" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="O20"/>
       <c r="P20"/>
     </row>
     <row r="21" spans="3:20">
-      <c r="C21"/>
-      <c r="D21"/>
-      <c r="E21"/>
+      <c r="C21" t="s">
+        <v>120</v>
+      </c>
+      <c r="E21">
+        <v>3</v>
+      </c>
       <c r="F21"/>
-      <c r="G21"/>
-      <c r="H21"/>
-      <c r="I21"/>
-      <c r="J21"/>
-      <c r="K21"/>
+      <c r="G21" s="26">
+        <f t="shared" ref="G21:K21" si="4">$E$21/3.6</f>
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="H21" s="26">
+        <f t="shared" si="4"/>
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="I21" s="26">
+        <f t="shared" si="4"/>
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="J21" s="26">
+        <f t="shared" si="4"/>
+        <v>0.83333333333333326</v>
+      </c>
+      <c r="K21" s="26">
+        <f t="shared" si="4"/>
+        <v>0.83333333333333326</v>
+      </c>
       <c r="L21"/>
-      <c r="M21"/>
-      <c r="N21"/>
+      <c r="M21" t="s">
+        <v>119</v>
+      </c>
+      <c r="N21" t="s">
+        <v>118</v>
+      </c>
       <c r="O21"/>
       <c r="P21"/>
     </row>
@@ -16783,55 +16786,53 @@
       <c r="D22"/>
       <c r="E22"/>
       <c r="F22"/>
-      <c r="G22" s="98">
-        <f t="shared" ref="G22" si="4">G18+G20</f>
-        <v>12.775231427006712</v>
-      </c>
-      <c r="H22" s="98">
-        <f t="shared" ref="H22:K22" si="5">H18+H20</f>
-        <v>13.844655136887908</v>
-      </c>
-      <c r="I22" s="98">
-        <f t="shared" si="5"/>
-        <v>20.699646648446279</v>
-      </c>
-      <c r="J22" s="98">
-        <f t="shared" si="5"/>
-        <v>24.100186765447592</v>
-      </c>
-      <c r="K22" s="98">
-        <f t="shared" si="5"/>
-        <v>27.970361406895258</v>
-      </c>
+      <c r="G22"/>
+      <c r="H22"/>
+      <c r="I22"/>
+      <c r="J22"/>
+      <c r="K22"/>
       <c r="L22"/>
-      <c r="M22" s="97" t="s">
-        <v>117</v>
-      </c>
-      <c r="N22" t="s">
-        <v>116</v>
-      </c>
+      <c r="M22"/>
+      <c r="N22"/>
       <c r="O22"/>
-      <c r="P22" t="s">
-        <v>115</v>
-      </c>
+      <c r="P22"/>
     </row>
     <row r="23" spans="3:20">
       <c r="C23"/>
       <c r="D23"/>
       <c r="E23"/>
       <c r="F23"/>
-      <c r="G23"/>
-      <c r="H23"/>
-      <c r="I23"/>
-      <c r="J23"/>
-      <c r="K23"/>
+      <c r="G23" s="98">
+        <f>G19+G21</f>
+        <v>12.775231427006712</v>
+      </c>
+      <c r="H23" s="98">
+        <f t="shared" ref="H23:K23" si="5">H19+H21</f>
+        <v>13.844655136887908</v>
+      </c>
+      <c r="I23" s="98">
+        <f t="shared" si="5"/>
+        <v>20.699646648446279</v>
+      </c>
+      <c r="J23" s="98">
+        <f t="shared" si="5"/>
+        <v>24.100186765447592</v>
+      </c>
+      <c r="K23" s="98">
+        <f t="shared" si="5"/>
+        <v>27.970361406895258</v>
+      </c>
       <c r="L23"/>
-      <c r="M23"/>
-      <c r="N23"/>
+      <c r="M23" s="97" t="s">
+        <v>117</v>
+      </c>
+      <c r="N23" t="s">
+        <v>116</v>
+      </c>
       <c r="O23"/>
-      <c r="P23"/>
-      <c r="Q23"/>
-      <c r="R23"/>
+      <c r="P23" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="24" spans="3:20">
       <c r="C24"/>
@@ -16841,10 +16842,10 @@
       <c r="G24"/>
       <c r="H24"/>
       <c r="I24"/>
-      <c r="J24" s="102"/>
-      <c r="K24" s="102"/>
-      <c r="L24" s="102"/>
-      <c r="M24" s="102"/>
+      <c r="J24"/>
+      <c r="K24"/>
+      <c r="L24"/>
+      <c r="M24"/>
       <c r="N24"/>
       <c r="O24"/>
       <c r="P24"/>
@@ -16859,10 +16860,10 @@
       <c r="G25"/>
       <c r="H25"/>
       <c r="I25"/>
-      <c r="J25"/>
-      <c r="K25"/>
-      <c r="L25"/>
-      <c r="M25"/>
+      <c r="J25" s="102"/>
+      <c r="K25" s="102"/>
+      <c r="L25" s="102"/>
+      <c r="M25" s="102"/>
       <c r="N25"/>
       <c r="O25"/>
       <c r="P25"/>
@@ -16904,8 +16905,6 @@
       <c r="P27"/>
       <c r="Q27"/>
       <c r="R27"/>
-      <c r="S27"/>
-      <c r="T27"/>
     </row>
     <row r="28" spans="3:20">
       <c r="C28"/>
@@ -17087,10 +17086,30 @@
       <c r="S36"/>
       <c r="T36"/>
     </row>
+    <row r="37" spans="3:20">
+      <c r="C37"/>
+      <c r="D37"/>
+      <c r="E37"/>
+      <c r="F37"/>
+      <c r="G37"/>
+      <c r="H37"/>
+      <c r="I37"/>
+      <c r="J37"/>
+      <c r="K37"/>
+      <c r="L37"/>
+      <c r="M37"/>
+      <c r="N37"/>
+      <c r="O37"/>
+      <c r="P37"/>
+      <c r="Q37"/>
+      <c r="R37"/>
+      <c r="S37"/>
+      <c r="T37"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="G7:K7"/>
-    <mergeCell ref="N7:O7"/>
+    <mergeCell ref="G8:K8"/>
+    <mergeCell ref="N8:O8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -34119,21 +34138,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010087B74FDAF7A4FB4D876E5EA45926113E" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="327522a6d5518d67d5f1063e9cc64cf0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3a32fc56-8470-4d77-ad86-bef2a7229878" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ffd5532d255be23b9fb13183c07e1fd0" ns2:_="">
     <xsd:import namespace="3a32fc56-8470-4d77-ad86-bef2a7229878"/>
@@ -34279,31 +34283,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1EBC224-6025-40B6-954C-A60FF473B45B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="3a32fc56-8470-4d77-ad86-bef2a7229878"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44F399E6-2CA4-4BC3-AE7C-3570BA9F00A0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F32A5943-069C-47E6-B7B1-1C4E8CC11B6B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -34319,4 +34314,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44F399E6-2CA4-4BC3-AE7C-3570BA9F00A0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1EBC224-6025-40B6-954C-A60FF473B45B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="3a32fc56-8470-4d77-ad86-bef2a7229878"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>